--- a/output/pdf_financials_xlsx/WATR.xlsx
+++ b/output/pdf_financials_xlsx/WATR.xlsx
@@ -3987,10 +3987,10 @@
         <v>5.694918</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>5.694918</v>
+        <v>5.962239</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>6.352822</v>
+        <v>7.008861</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>7.343833</v>
@@ -15474,7 +15474,11 @@
           <t>Warrants reserved 583,918</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -17172,7 +17176,11 @@
           <t>WARRANT RESERVE (note 10) 656,039</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WATR.xlsx
+++ b/output/pdf_financials_xlsx/WATR.xlsx
@@ -1728,7 +1728,7 @@
         <v>0.12448</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.097687</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.635301</v>
@@ -1802,7 +1802,7 @@
         <v>0.12448</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.097687</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.635301</v>
@@ -2246,7 +2246,7 @@
         <v>0.00594</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.185877</v>
+        <v>0.08819</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.397035</v>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -31038,7 +31038,11 @@
           <t>General and administration expenses (Note 16)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WATR.xlsx
+++ b/output/pdf_financials_xlsx/WATR.xlsx
@@ -4270,10 +4270,10 @@
         <v>0.055997</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0.037575</v>
+        <v>0.026924</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.012747</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -25718,7 +25718,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
